--- a/dados_açucar.xlsx
+++ b/dados_açucar.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7403566dc7686ca4/cHALLENGE lek/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7403566dc7686ca4/Dados Desafio LEK/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DE1DA0FC-3AD9-40BA-80AD-108827EB83F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="8_{DE1DA0FC-3AD9-40BA-80AD-108827EB83F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{97408219-1A17-4A59-9C3E-E8D2923B95AE}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7BD2626C-80E7-43AA-951D-A66104C3FAAC}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="40">
   <si>
     <t>Commodity</t>
   </si>
@@ -638,13 +638,10 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1127,1064 +1124,1106 @@
       </c>
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D2" s="2">
         <v>17.100000000000001</v>
       </c>
-      <c r="E2" s="3">
+      <c r="E2" s="2">
         <v>20.399999999999999</v>
       </c>
-      <c r="F2" s="3">
+      <c r="F2" s="2">
         <v>23.81</v>
       </c>
-      <c r="G2" s="3">
+      <c r="G2" s="2">
         <v>26.4</v>
       </c>
-      <c r="H2" s="3">
+      <c r="H2" s="2">
         <v>28.175000000000001</v>
       </c>
-      <c r="I2" s="3">
+      <c r="I2" s="2">
         <v>26.85</v>
       </c>
-      <c r="J2" s="3">
+      <c r="J2" s="2">
         <v>31.45</v>
       </c>
-      <c r="K2" s="3">
+      <c r="K2" s="2">
         <v>31.6</v>
       </c>
-      <c r="L2" s="3">
+      <c r="L2" s="2">
         <v>31.85</v>
       </c>
-      <c r="M2" s="3">
+      <c r="M2" s="2">
         <v>36.4</v>
       </c>
-      <c r="N2" s="3">
+      <c r="N2" s="2">
         <v>38.35</v>
       </c>
-      <c r="O2" s="3">
+      <c r="O2" s="2">
         <v>36.15</v>
       </c>
-      <c r="P2" s="3">
+      <c r="P2" s="2">
         <v>38.6</v>
       </c>
-      <c r="Q2" s="3">
+      <c r="Q2" s="2">
         <v>37.799999999999997</v>
       </c>
-      <c r="R2" s="3">
+      <c r="R2" s="2">
         <v>35.950000000000003</v>
       </c>
-      <c r="S2" s="3">
+      <c r="S2" s="2">
         <v>34.65</v>
       </c>
-      <c r="T2" s="3">
+      <c r="T2" s="2">
         <v>39.15</v>
       </c>
-      <c r="U2" s="3">
+      <c r="U2" s="2">
         <v>38.869999999999997</v>
       </c>
-      <c r="V2" s="3">
+      <c r="V2" s="2">
         <v>29.5</v>
       </c>
-      <c r="W2" s="3">
+      <c r="W2" s="2">
         <v>30.3</v>
       </c>
-      <c r="X2" s="3">
+      <c r="X2" s="2">
         <v>42.05</v>
       </c>
-      <c r="Y2" s="3">
+      <c r="Y2" s="2">
         <v>35.450000000000003</v>
       </c>
-      <c r="Z2" s="3">
+      <c r="Z2" s="2">
         <v>38.049999999999997</v>
       </c>
-      <c r="AA2" s="3">
+      <c r="AA2" s="2">
         <v>45.543999999999997</v>
       </c>
-      <c r="AB2" s="3">
+      <c r="AB2" s="2">
         <v>43.7</v>
       </c>
-      <c r="AC2" s="3">
+      <c r="AC2" s="2">
         <v>44.386000000000003</v>
       </c>
-      <c r="AD2" s="3" t="s">
+      <c r="AD2" s="2" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="3" t="s">
+      <c r="A3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="2">
         <v>17.100000000000001</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3" s="2">
         <v>20.399999999999999</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F3" s="2">
         <v>23.81</v>
       </c>
-      <c r="G3" s="3">
+      <c r="G3" s="2">
         <v>26.4</v>
       </c>
-      <c r="H3" s="3">
+      <c r="H3" s="2">
         <v>28.175000000000001</v>
       </c>
-      <c r="I3" s="3">
+      <c r="I3" s="2">
         <v>26.85</v>
       </c>
-      <c r="J3" s="3">
+      <c r="J3" s="2">
         <v>31.45</v>
       </c>
-      <c r="K3" s="3">
+      <c r="K3" s="2">
         <v>31.6</v>
       </c>
-      <c r="L3" s="3">
+      <c r="L3" s="2">
         <v>31.85</v>
       </c>
-      <c r="M3" s="3">
+      <c r="M3" s="2">
         <v>36.4</v>
       </c>
-      <c r="N3" s="3">
+      <c r="N3" s="2">
         <v>38.35</v>
       </c>
-      <c r="O3" s="3">
+      <c r="O3" s="2">
         <v>36.15</v>
       </c>
-      <c r="P3" s="3">
+      <c r="P3" s="2">
         <v>38.6</v>
       </c>
-      <c r="Q3" s="3">
+      <c r="Q3" s="2">
         <v>37.799999999999997</v>
       </c>
-      <c r="R3" s="3">
+      <c r="R3" s="2">
         <v>35.950000000000003</v>
       </c>
-      <c r="S3" s="3">
+      <c r="S3" s="2">
         <v>34.65</v>
       </c>
-      <c r="T3" s="3">
+      <c r="T3" s="2">
         <v>39.15</v>
       </c>
-      <c r="U3" s="3">
+      <c r="U3" s="2">
         <v>38.869999999999997</v>
       </c>
-      <c r="V3" s="3">
+      <c r="V3" s="2">
         <v>29.5</v>
       </c>
-      <c r="W3" s="3">
+      <c r="W3" s="2">
         <v>30.3</v>
       </c>
-      <c r="X3" s="3">
+      <c r="X3" s="2">
         <v>42.05</v>
       </c>
-      <c r="Y3" s="3">
+      <c r="Y3" s="2">
         <v>35.450000000000003</v>
       </c>
-      <c r="Z3" s="3">
+      <c r="Z3" s="2">
         <v>38.049999999999997</v>
       </c>
-      <c r="AA3" s="3">
+      <c r="AA3" s="2">
         <v>45.543999999999997</v>
       </c>
-      <c r="AB3" s="3">
+      <c r="AB3" s="2">
         <v>43.7</v>
       </c>
-      <c r="AC3" s="3">
+      <c r="AC3" s="2">
         <v>44.386000000000003</v>
       </c>
-      <c r="AD3" s="3" t="s">
+      <c r="AD3" s="2" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="3" t="s">
+      <c r="A4" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D4" s="3">
-        <v>0</v>
-      </c>
-      <c r="E4" s="3">
-        <v>0</v>
-      </c>
-      <c r="F4" s="3">
-        <v>0</v>
-      </c>
-      <c r="G4" s="3">
-        <v>0</v>
-      </c>
-      <c r="H4" s="3">
-        <v>0</v>
-      </c>
-      <c r="I4" s="3">
-        <v>0</v>
-      </c>
-      <c r="J4" s="3">
-        <v>0</v>
-      </c>
-      <c r="K4" s="3">
-        <v>0</v>
-      </c>
-      <c r="L4" s="3">
-        <v>0</v>
-      </c>
-      <c r="M4" s="3">
-        <v>0</v>
-      </c>
-      <c r="N4" s="3">
-        <v>0</v>
-      </c>
-      <c r="O4" s="3">
-        <v>0</v>
-      </c>
-      <c r="P4" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="3">
-        <v>0</v>
-      </c>
-      <c r="R4" s="3">
-        <v>0</v>
-      </c>
-      <c r="S4" s="3">
-        <v>0</v>
-      </c>
-      <c r="T4" s="3">
-        <v>0</v>
-      </c>
-      <c r="U4" s="3">
-        <v>0</v>
-      </c>
-      <c r="V4" s="3">
-        <v>0</v>
-      </c>
-      <c r="W4" s="3">
-        <v>0</v>
-      </c>
-      <c r="X4" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y4" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z4" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA4" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB4" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC4" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD4" s="3" t="s">
+      <c r="D4" s="2">
+        <v>0</v>
+      </c>
+      <c r="E4" s="2">
+        <v>0</v>
+      </c>
+      <c r="F4" s="2">
+        <v>0</v>
+      </c>
+      <c r="G4" s="2">
+        <v>0</v>
+      </c>
+      <c r="H4" s="2">
+        <v>0</v>
+      </c>
+      <c r="I4" s="2">
+        <v>0</v>
+      </c>
+      <c r="J4" s="2">
+        <v>0</v>
+      </c>
+      <c r="K4" s="2">
+        <v>0</v>
+      </c>
+      <c r="L4" s="2">
+        <v>0</v>
+      </c>
+      <c r="M4" s="2">
+        <v>0</v>
+      </c>
+      <c r="N4" s="2">
+        <v>0</v>
+      </c>
+      <c r="O4" s="2">
+        <v>0</v>
+      </c>
+      <c r="P4" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="2">
+        <v>0</v>
+      </c>
+      <c r="R4" s="2">
+        <v>0</v>
+      </c>
+      <c r="S4" s="2">
+        <v>0</v>
+      </c>
+      <c r="T4" s="2">
+        <v>0</v>
+      </c>
+      <c r="U4" s="2">
+        <v>0</v>
+      </c>
+      <c r="V4" s="2">
+        <v>0</v>
+      </c>
+      <c r="W4" s="2">
+        <v>0</v>
+      </c>
+      <c r="X4" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z4" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA4" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD4" s="2" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="3" t="s">
+      <c r="A5" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="2">
         <v>7.7</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="2">
         <v>11.6</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F5" s="2">
         <v>14</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G5" s="2">
         <v>15.24</v>
       </c>
-      <c r="H5" s="3">
+      <c r="H5" s="2">
         <v>18.02</v>
       </c>
-      <c r="I5" s="3">
+      <c r="I5" s="2">
         <v>17.09</v>
       </c>
-      <c r="J5" s="3">
+      <c r="J5" s="2">
         <v>20.85</v>
       </c>
-      <c r="K5" s="3">
+      <c r="K5" s="2">
         <v>19.5</v>
       </c>
-      <c r="L5" s="3">
+      <c r="L5" s="2">
         <v>21.55</v>
       </c>
-      <c r="M5" s="3">
+      <c r="M5" s="2">
         <v>24.3</v>
       </c>
-      <c r="N5" s="3">
+      <c r="N5" s="2">
         <v>25.8</v>
       </c>
-      <c r="O5" s="3">
+      <c r="O5" s="2">
         <v>24.65</v>
       </c>
-      <c r="P5" s="3">
+      <c r="P5" s="2">
         <v>27.65</v>
       </c>
-      <c r="Q5" s="3">
+      <c r="Q5" s="2">
         <v>26.2</v>
       </c>
-      <c r="R5" s="3">
+      <c r="R5" s="2">
         <v>23.95</v>
       </c>
-      <c r="S5" s="3">
+      <c r="S5" s="2">
         <v>24.35</v>
       </c>
-      <c r="T5" s="3">
+      <c r="T5" s="2">
         <v>28.5</v>
       </c>
-      <c r="U5" s="3">
+      <c r="U5" s="2">
         <v>28.2</v>
       </c>
-      <c r="V5" s="3">
+      <c r="V5" s="2">
         <v>19.600000000000001</v>
       </c>
-      <c r="W5" s="3">
+      <c r="W5" s="2">
         <v>19.28</v>
       </c>
-      <c r="X5" s="3">
+      <c r="X5" s="2">
         <v>32.15</v>
       </c>
-      <c r="Y5" s="3">
+      <c r="Y5" s="2">
         <v>25.95</v>
       </c>
-      <c r="Z5" s="3">
+      <c r="Z5" s="2">
         <v>28.2</v>
       </c>
-      <c r="AA5" s="3">
+      <c r="AA5" s="2">
         <v>35.973999999999997</v>
       </c>
-      <c r="AB5" s="3">
+      <c r="AB5" s="2">
         <v>34.89</v>
       </c>
-      <c r="AC5" s="3">
+      <c r="AC5" s="2">
         <v>35.700000000000003</v>
       </c>
-      <c r="AD5" s="3" t="s">
+      <c r="AD5" s="2" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="3" t="s">
+      <c r="A6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="2">
         <v>9.25</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6" s="2">
         <v>9.4499999999999993</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F6" s="2">
         <v>9.75</v>
       </c>
-      <c r="G6" s="3">
+      <c r="G6" s="2">
         <v>10.4</v>
       </c>
-      <c r="H6" s="3">
+      <c r="H6" s="2">
         <v>10.6</v>
       </c>
-      <c r="I6" s="3">
+      <c r="I6" s="2">
         <v>10.63</v>
       </c>
-      <c r="J6" s="3">
+      <c r="J6" s="2">
         <v>10.8</v>
       </c>
-      <c r="K6" s="3">
+      <c r="K6" s="2">
         <v>11.4</v>
       </c>
-      <c r="L6" s="3">
+      <c r="L6" s="2">
         <v>11.65</v>
       </c>
-      <c r="M6" s="3">
+      <c r="M6" s="2">
         <v>11.8</v>
       </c>
-      <c r="N6" s="3">
+      <c r="N6" s="2">
         <v>11.455</v>
       </c>
-      <c r="O6" s="3">
+      <c r="O6" s="2">
         <v>11.5</v>
       </c>
-      <c r="P6" s="3">
+      <c r="P6" s="2">
         <v>11.2</v>
       </c>
-      <c r="Q6" s="3">
+      <c r="Q6" s="2">
         <v>11.26</v>
       </c>
-      <c r="R6" s="3">
+      <c r="R6" s="2">
         <v>11.4</v>
       </c>
-      <c r="S6" s="3">
+      <c r="S6" s="2">
         <v>10.5</v>
       </c>
-      <c r="T6" s="3">
+      <c r="T6" s="2">
         <v>10.55</v>
       </c>
-      <c r="U6" s="3">
+      <c r="U6" s="2">
         <v>10.6</v>
       </c>
-      <c r="V6" s="3">
+      <c r="V6" s="2">
         <v>10.6</v>
       </c>
-      <c r="W6" s="3">
+      <c r="W6" s="2">
         <v>10.65</v>
       </c>
-      <c r="X6" s="3">
+      <c r="X6" s="2">
         <v>10.15</v>
       </c>
-      <c r="Y6" s="3">
+      <c r="Y6" s="2">
         <v>9.5</v>
       </c>
-      <c r="Z6" s="3">
+      <c r="Z6" s="2">
         <v>9.5</v>
       </c>
-      <c r="AA6" s="3">
+      <c r="AA6" s="2">
         <v>9.5</v>
       </c>
-      <c r="AB6" s="3">
+      <c r="AB6" s="2">
         <v>9</v>
       </c>
-      <c r="AC6" s="3">
+      <c r="AC6" s="2">
         <v>9</v>
       </c>
-      <c r="AD6" s="3" t="s">
+      <c r="AD6" s="2" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="3" t="s">
+      <c r="A7" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="2">
         <v>860</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7" s="2">
         <v>210</v>
       </c>
-      <c r="F7" s="3">
+      <c r="F7" s="2">
         <v>270</v>
       </c>
-      <c r="G7" s="3">
+      <c r="G7" s="2">
         <v>1.03</v>
       </c>
-      <c r="H7" s="3">
+      <c r="H7" s="2">
         <v>585</v>
       </c>
-      <c r="I7" s="3">
+      <c r="I7" s="2">
         <v>-285</v>
       </c>
-      <c r="J7" s="3">
+      <c r="J7" s="2">
         <v>-485</v>
       </c>
-      <c r="K7" s="3">
+      <c r="K7" s="2">
         <v>215</v>
       </c>
-      <c r="L7" s="3">
+      <c r="L7" s="2">
         <v>-1.135</v>
       </c>
-      <c r="M7" s="3">
+      <c r="M7" s="2">
         <v>-835</v>
       </c>
-      <c r="N7" s="3">
+      <c r="N7" s="2">
         <v>260</v>
       </c>
-      <c r="O7" s="3">
+      <c r="O7" s="2">
         <v>260</v>
       </c>
-      <c r="P7" s="3">
+      <c r="P7" s="2">
         <v>10</v>
       </c>
-      <c r="Q7" s="3">
+      <c r="Q7" s="2">
         <v>350</v>
       </c>
-      <c r="R7" s="3">
+      <c r="R7" s="2">
         <v>950</v>
       </c>
-      <c r="S7" s="3">
+      <c r="S7" s="2">
         <v>750</v>
       </c>
-      <c r="T7" s="3">
+      <c r="T7" s="2">
         <v>850</v>
       </c>
-      <c r="U7" s="3">
+      <c r="U7" s="2">
         <v>920</v>
       </c>
-      <c r="V7" s="3">
+      <c r="V7" s="2">
         <v>220</v>
       </c>
-      <c r="W7" s="3">
+      <c r="W7" s="2">
         <v>590</v>
       </c>
-      <c r="X7" s="3">
+      <c r="X7" s="2">
         <v>340</v>
       </c>
-      <c r="Y7" s="3">
+      <c r="Y7" s="2">
         <v>340</v>
       </c>
-      <c r="Z7" s="3">
+      <c r="Z7" s="2">
         <v>690</v>
       </c>
-      <c r="AA7" s="3">
+      <c r="AA7" s="2">
         <v>760</v>
       </c>
-      <c r="AB7" s="3">
+      <c r="AB7" s="2">
         <v>570</v>
       </c>
-      <c r="AC7" s="3">
+      <c r="AC7" s="2">
         <v>256</v>
       </c>
-      <c r="AD7" s="3" t="s">
+      <c r="AD7" s="2" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A8" s="2"/>
-      <c r="B8" s="3" t="s">
+      <c r="A8" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="2">
         <v>94.111000000000004</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8" s="2">
         <v>101.80500000000001</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F8" s="2">
         <v>111.601</v>
       </c>
-      <c r="G8" s="3">
+      <c r="G8" s="2">
         <v>107.9</v>
       </c>
-      <c r="H8" s="3">
+      <c r="H8" s="2">
         <v>103.60899999999999</v>
       </c>
-      <c r="I8" s="3">
+      <c r="I8" s="2">
         <v>106.81399999999999</v>
       </c>
-      <c r="J8" s="3">
+      <c r="J8" s="2">
         <v>127.983</v>
       </c>
-      <c r="K8" s="3">
+      <c r="K8" s="2">
         <v>130.80199999999999</v>
       </c>
-      <c r="L8" s="3">
+      <c r="L8" s="2">
         <v>113.837</v>
       </c>
-      <c r="M8" s="3">
+      <c r="M8" s="2">
         <v>120.14</v>
       </c>
-      <c r="N8" s="3">
+      <c r="N8" s="2">
         <v>130.21700000000001</v>
       </c>
-      <c r="O8" s="3">
+      <c r="O8" s="2">
         <v>133.73699999999999</v>
       </c>
-      <c r="P8" s="3">
+      <c r="P8" s="2">
         <v>141.46100000000001</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="Q8" s="2">
         <v>142.29300000000001</v>
       </c>
-      <c r="R8" s="3">
+      <c r="R8" s="2">
         <v>140.88900000000001</v>
       </c>
-      <c r="S8" s="3">
+      <c r="S8" s="2">
         <v>131.55600000000001</v>
       </c>
-      <c r="T8" s="3">
+      <c r="T8" s="2">
         <v>133.97900000000001</v>
       </c>
-      <c r="U8" s="3">
+      <c r="U8" s="2">
         <v>150.511</v>
       </c>
-      <c r="V8" s="3">
+      <c r="V8" s="2">
         <v>139.57900000000001</v>
       </c>
-      <c r="W8" s="3">
+      <c r="W8" s="2">
         <v>125.863</v>
       </c>
-      <c r="X8" s="3">
+      <c r="X8" s="2">
         <v>142.94300000000001</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Y8" s="2">
         <v>142.517</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="Z8" s="2">
         <v>143.73500000000001</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AA8" s="2">
         <v>141.12700000000001</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AB8" s="2">
         <v>139.75700000000001</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AC8" s="2">
         <v>149.60499999999999</v>
       </c>
-      <c r="AD8" s="3" t="s">
+      <c r="AD8" s="2" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="3" t="s">
+      <c r="A9" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="2">
         <v>130.76400000000001</v>
       </c>
-      <c r="E9" s="3">
+      <c r="E9" s="2">
         <v>134.398</v>
       </c>
-      <c r="F9" s="3">
+      <c r="F9" s="2">
         <v>148.55199999999999</v>
       </c>
-      <c r="G9" s="3">
+      <c r="G9" s="2">
         <v>142.48699999999999</v>
       </c>
-      <c r="H9" s="3">
+      <c r="H9" s="2">
         <v>140.73400000000001</v>
       </c>
-      <c r="I9" s="3">
+      <c r="I9" s="2">
         <v>144.303</v>
       </c>
-      <c r="J9" s="3">
+      <c r="J9" s="2">
         <v>164.27799999999999</v>
       </c>
-      <c r="K9" s="3">
+      <c r="K9" s="2">
         <v>163.25700000000001</v>
       </c>
-      <c r="L9" s="3">
+      <c r="L9" s="2">
         <v>143.833</v>
       </c>
-      <c r="M9" s="3">
+      <c r="M9" s="2">
         <v>153.35499999999999</v>
       </c>
-      <c r="N9" s="3">
+      <c r="N9" s="2">
         <v>162.1</v>
       </c>
-      <c r="O9" s="3">
+      <c r="O9" s="2">
         <v>172.19300000000001</v>
       </c>
-      <c r="P9" s="3">
+      <c r="P9" s="2">
         <v>177.898</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="Q9" s="2">
         <v>175.93299999999999</v>
       </c>
-      <c r="R9" s="3">
+      <c r="R9" s="2">
         <v>177.756</v>
       </c>
-      <c r="S9" s="3">
+      <c r="S9" s="2">
         <v>164.97200000000001</v>
       </c>
-      <c r="T9" s="3">
+      <c r="T9" s="2">
         <v>172.143</v>
       </c>
-      <c r="U9" s="3">
+      <c r="U9" s="2">
         <v>194.20599999999999</v>
       </c>
-      <c r="V9" s="3">
+      <c r="V9" s="2">
         <v>179.13200000000001</v>
       </c>
-      <c r="W9" s="3">
+      <c r="W9" s="2">
         <v>166.55500000000001</v>
       </c>
-      <c r="X9" s="3">
+      <c r="X9" s="2">
         <v>180.262</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Y9" s="2">
         <v>180.721</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="Z9" s="2">
         <v>179.262</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AA9" s="2">
         <v>180.2</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AB9" s="2">
         <v>180.96799999999999</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AC9" s="2">
         <v>189.25899999999999</v>
       </c>
-      <c r="AD9" s="3" t="s">
+      <c r="AD9" s="2" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="3" t="s">
+      <c r="A10" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="2">
         <v>40.378999999999998</v>
       </c>
-      <c r="E10" s="3">
+      <c r="E10" s="2">
         <v>39.695</v>
       </c>
-      <c r="F10" s="3">
+      <c r="F10" s="2">
         <v>41.698999999999998</v>
       </c>
-      <c r="G10" s="3">
+      <c r="G10" s="2">
         <v>41.256</v>
       </c>
-      <c r="H10" s="3">
+      <c r="H10" s="2">
         <v>45.478000000000002</v>
       </c>
-      <c r="I10" s="3">
+      <c r="I10" s="2">
         <v>44.723999999999997</v>
       </c>
-      <c r="J10" s="3">
+      <c r="J10" s="2">
         <v>44.142000000000003</v>
       </c>
-      <c r="K10" s="3">
+      <c r="K10" s="2">
         <v>44.959000000000003</v>
       </c>
-      <c r="L10" s="3">
+      <c r="L10" s="2">
         <v>42.335000000000001</v>
       </c>
-      <c r="M10" s="3">
+      <c r="M10" s="2">
         <v>48.279000000000003</v>
       </c>
-      <c r="N10" s="3">
+      <c r="N10" s="2">
         <v>49.122</v>
       </c>
-      <c r="O10" s="3">
+      <c r="O10" s="2">
         <v>48.564999999999998</v>
       </c>
-      <c r="P10" s="3">
+      <c r="P10" s="2">
         <v>51.447000000000003</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="Q10" s="2">
         <v>51.451999999999998</v>
       </c>
-      <c r="R10" s="3">
+      <c r="R10" s="2">
         <v>50.250999999999998</v>
       </c>
-      <c r="S10" s="3">
+      <c r="S10" s="2">
         <v>54.646999999999998</v>
       </c>
-      <c r="T10" s="3">
+      <c r="T10" s="2">
         <v>55.418999999999997</v>
       </c>
-      <c r="U10" s="3">
+      <c r="U10" s="2">
         <v>55.685000000000002</v>
       </c>
-      <c r="V10" s="3">
+      <c r="V10" s="2">
         <v>53.189</v>
       </c>
-      <c r="W10" s="3">
+      <c r="W10" s="2">
         <v>54.097000000000001</v>
       </c>
-      <c r="X10" s="3">
+      <c r="X10" s="2">
         <v>58.286000000000001</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Y10" s="2">
         <v>56.378999999999998</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="Z10" s="2">
         <v>58.716000000000001</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AA10" s="2">
         <v>59.802</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AB10" s="2">
         <v>56.246000000000002</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AC10" s="2">
         <v>57.542000000000002</v>
       </c>
-      <c r="AD10" s="3" t="s">
+      <c r="AD10" s="2" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="3" t="s">
+      <c r="A11" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D11" s="2">
         <v>38.314999999999998</v>
       </c>
-      <c r="E11" s="3">
+      <c r="E11" s="2">
         <v>42.332999999999998</v>
       </c>
-      <c r="F11" s="3">
+      <c r="F11" s="2">
         <v>47.204999999999998</v>
       </c>
-      <c r="G11" s="3">
+      <c r="G11" s="2">
         <v>46.536999999999999</v>
       </c>
-      <c r="H11" s="3">
+      <c r="H11" s="2">
         <v>46.951000000000001</v>
       </c>
-      <c r="I11" s="3">
+      <c r="I11" s="2">
         <v>49.533999999999999</v>
       </c>
-      <c r="J11" s="3">
+      <c r="J11" s="2">
         <v>50.76</v>
       </c>
-      <c r="K11" s="3">
+      <c r="K11" s="2">
         <v>50.625</v>
       </c>
-      <c r="L11" s="3">
+      <c r="L11" s="2">
         <v>44.962000000000003</v>
       </c>
-      <c r="M11" s="3">
+      <c r="M11" s="2">
         <v>48.328000000000003</v>
       </c>
-      <c r="N11" s="3">
+      <c r="N11" s="2">
         <v>53.939</v>
       </c>
-      <c r="O11" s="3">
+      <c r="O11" s="2">
         <v>54.996000000000002</v>
       </c>
-      <c r="P11" s="3">
+      <c r="P11" s="2">
         <v>55.741999999999997</v>
       </c>
-      <c r="Q11" s="3">
+      <c r="Q11" s="2">
         <v>57.951000000000001</v>
       </c>
-      <c r="R11" s="3">
+      <c r="R11" s="2">
         <v>55.033000000000001</v>
       </c>
-      <c r="S11" s="3">
+      <c r="S11" s="2">
         <v>54.186999999999998</v>
       </c>
-      <c r="T11" s="3">
+      <c r="T11" s="2">
         <v>60.046999999999997</v>
       </c>
-      <c r="U11" s="3">
+      <c r="U11" s="2">
         <v>65.867999999999995</v>
       </c>
-      <c r="V11" s="3">
+      <c r="V11" s="2">
         <v>58.284999999999997</v>
       </c>
-      <c r="W11" s="3">
+      <c r="W11" s="2">
         <v>53.524000000000001</v>
       </c>
-      <c r="X11" s="3">
+      <c r="X11" s="2">
         <v>64.033000000000001</v>
       </c>
-      <c r="Y11" s="3">
+      <c r="Y11" s="2">
         <v>64.664000000000001</v>
       </c>
-      <c r="Z11" s="3">
+      <c r="Z11" s="2">
         <v>62.008000000000003</v>
       </c>
-      <c r="AA11" s="3">
+      <c r="AA11" s="2">
         <v>62.936999999999998</v>
       </c>
-      <c r="AB11" s="3">
+      <c r="AB11" s="2">
         <v>63.387999999999998</v>
       </c>
-      <c r="AC11" s="3">
+      <c r="AC11" s="2">
         <v>66.001000000000005</v>
       </c>
-      <c r="AD11" s="3" t="s">
+      <c r="AD11" s="2" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="3" t="s">
+      <c r="A12" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="2">
         <v>130.392</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="2">
         <v>134.98500000000001</v>
       </c>
-      <c r="F12" s="3">
+      <c r="F12" s="2">
         <v>139.08199999999999</v>
       </c>
-      <c r="G12" s="3">
+      <c r="G12" s="2">
         <v>139.744</v>
       </c>
-      <c r="H12" s="3">
+      <c r="H12" s="2">
         <v>142.577</v>
       </c>
-      <c r="I12" s="3">
+      <c r="I12" s="2">
         <v>143.75399999999999</v>
       </c>
-      <c r="J12" s="3">
+      <c r="J12" s="2">
         <v>151.399</v>
       </c>
-      <c r="K12" s="3">
+      <c r="K12" s="2">
         <v>151.34700000000001</v>
       </c>
-      <c r="L12" s="3">
+      <c r="L12" s="2">
         <v>154.59800000000001</v>
       </c>
-      <c r="M12" s="3">
+      <c r="M12" s="2">
         <v>155.226</v>
       </c>
-      <c r="N12" s="3">
+      <c r="N12" s="2">
         <v>156.18799999999999</v>
       </c>
-      <c r="O12" s="3">
+      <c r="O12" s="2">
         <v>160.21700000000001</v>
       </c>
-      <c r="P12" s="3">
+      <c r="P12" s="2">
         <v>166.43700000000001</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="Q12" s="2">
         <v>166.96</v>
       </c>
-      <c r="R12" s="3">
+      <c r="R12" s="2">
         <v>168.839</v>
       </c>
-      <c r="S12" s="3">
+      <c r="S12" s="2">
         <v>169.798</v>
       </c>
-      <c r="T12" s="3">
+      <c r="T12" s="2">
         <v>169.92400000000001</v>
       </c>
-      <c r="U12" s="3">
+      <c r="U12" s="2">
         <v>174.41300000000001</v>
       </c>
-      <c r="V12" s="3">
+      <c r="V12" s="2">
         <v>172.78</v>
       </c>
-      <c r="W12" s="3">
+      <c r="W12" s="2">
         <v>172.137</v>
       </c>
-      <c r="X12" s="3">
+      <c r="X12" s="2">
         <v>172.083</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Y12" s="2">
         <v>174.97399999999999</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="Z12" s="2">
         <v>177.47</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AA12" s="2">
         <v>177.691</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AB12" s="2">
         <v>176.37700000000001</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AC12" s="2">
         <v>178.65700000000001</v>
       </c>
-      <c r="AD12" s="3" t="s">
+      <c r="AD12" s="2" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="3" t="s">
+      <c r="A13" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D13" s="3">
+      <c r="D13" s="2">
         <v>39.869</v>
       </c>
-      <c r="E13" s="3">
+      <c r="E13" s="2">
         <v>36.643999999999998</v>
       </c>
-      <c r="F13" s="3">
+      <c r="F13" s="2">
         <v>40.607999999999997</v>
       </c>
-      <c r="G13" s="3">
+      <c r="G13" s="2">
         <v>38.07</v>
       </c>
-      <c r="H13" s="3">
+      <c r="H13" s="2">
         <v>34.753999999999998</v>
       </c>
-      <c r="I13" s="3">
+      <c r="I13" s="2">
         <v>30.492999999999999</v>
       </c>
-      <c r="J13" s="3">
+      <c r="J13" s="2">
         <v>36.753999999999998</v>
       </c>
-      <c r="K13" s="3">
+      <c r="K13" s="2">
         <v>42.997999999999998</v>
       </c>
-      <c r="L13" s="3">
+      <c r="L13" s="2">
         <v>29.606000000000002</v>
       </c>
-      <c r="M13" s="3">
+      <c r="M13" s="2">
         <v>27.686</v>
       </c>
-      <c r="N13" s="3">
+      <c r="N13" s="2">
         <v>28.780999999999999</v>
       </c>
-      <c r="O13" s="3">
+      <c r="O13" s="2">
         <v>34.326000000000001</v>
       </c>
-      <c r="P13" s="3">
+      <c r="P13" s="2">
         <v>41.491999999999997</v>
       </c>
-      <c r="Q13" s="3">
+      <c r="Q13" s="2">
         <v>43.966000000000001</v>
       </c>
-      <c r="R13" s="3">
+      <c r="R13" s="2">
         <v>48.100999999999999</v>
       </c>
-      <c r="S13" s="3">
+      <c r="S13" s="2">
         <v>43.734999999999999</v>
       </c>
-      <c r="T13" s="3">
+      <c r="T13" s="2">
         <v>41.326000000000001</v>
       </c>
-      <c r="U13" s="3">
+      <c r="U13" s="2">
         <v>50.936</v>
       </c>
-      <c r="V13" s="3">
+      <c r="V13" s="2">
         <v>52.192</v>
       </c>
-      <c r="W13" s="3">
+      <c r="W13" s="2">
         <v>47.183</v>
       </c>
-      <c r="X13" s="3">
+      <c r="X13" s="2">
         <v>49.615000000000002</v>
       </c>
-      <c r="Y13" s="3">
+      <c r="Y13" s="2">
         <v>47.076999999999998</v>
       </c>
-      <c r="Z13" s="3">
+      <c r="Z13" s="2">
         <v>45.576999999999998</v>
       </c>
-      <c r="AA13" s="3">
+      <c r="AA13" s="2">
         <v>44.951000000000001</v>
       </c>
-      <c r="AB13" s="3">
+      <c r="AB13" s="2">
         <v>42.4</v>
       </c>
-      <c r="AC13" s="3">
+      <c r="AC13" s="2">
         <v>44.542999999999999</v>
       </c>
-      <c r="AD13" s="3" t="s">
+      <c r="AD13" s="2" t="s">
         <v>33</v>
       </c>
     </row>
